--- a/data/leaderboard_snapshot.xlsx
+++ b/data/leaderboard_snapshot.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1"/>
+  <dimension ref="A1:B21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -439,6 +439,206 @@
         <is>
           <t>score</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Sooraj</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Rajeev</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Anoop N</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Abeesh</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Vipin Raj</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Vipin M B</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Vineeth</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Sikha</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Saneesh</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Rajeesh</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Nikhil Raj</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Muhammedali</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Lakshmi M S</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Jimson</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Jidhulal</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Gijo</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Bejoy</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Ashish</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Anoop M K</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Vijay</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -452,7 +652,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -482,6 +682,926 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>13</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Group A - Mexico vs South Africa (Group Stage) - Winners</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Abeesh</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Mexico</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>13</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Group A - Mexico vs South Africa (Group Stage) - Winners</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Anoop M K</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Mexico</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>13</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Group A - Mexico vs South Africa (Group Stage) - Winners</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Anoop N</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Mexico</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>13</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Group A - Mexico vs South Africa (Group Stage) - Winners</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ashish</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Mexico</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>13</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Group A - Mexico vs South Africa (Group Stage) - Winners</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Bejoy</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Mexico</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>13</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Group A - Mexico vs South Africa (Group Stage) - Winners</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Gijo</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Mexico</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>13</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Group A - Mexico vs South Africa (Group Stage) - Winners</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Jidhulal</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Mexico</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>13</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Group A - Mexico vs South Africa (Group Stage) - Winners</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Jimson</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Mexico</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>13</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Group A - Mexico vs South Africa (Group Stage) - Winners</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Lakshmi M S</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Mexico</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>13</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Group A - Mexico vs South Africa (Group Stage) - Winners</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Muhammedali</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Mexico</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>13</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Group A - Mexico vs South Africa (Group Stage) - Winners</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Nikhil Raj</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Mexico</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>13</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Group A - Mexico vs South Africa (Group Stage) - Winners</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Rajeesh</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Mexico</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Group A - Mexico vs South Africa (Group Stage) - Winners</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Rajeev</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Mexico</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Group A - Mexico vs South Africa (Group Stage) - Winners</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Saneesh</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Mexico</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>13</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Group A - Mexico vs South Africa (Group Stage) - Winners</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Sikha</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Mexico</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>13</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Group A - Mexico vs South Africa (Group Stage) - Winners</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Sooraj</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Mexico</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>13</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Group A - Mexico vs South Africa (Group Stage) - Winners</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Vijay</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Draw</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>13</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Group A - Mexico vs South Africa (Group Stage) - Winners</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Vineeth</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Mexico</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>13</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Group A - Mexico vs South Africa (Group Stage) - Winners</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Vipin M B</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Mexico</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>13</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Group A - Mexico vs South Africa (Group Stage) - Winners</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Vipin Raj</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Mexico</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>18</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Group A - Czechia vs Korea Republic (Group Stage) - Winners</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Abeesh</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Korea Republic</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>18</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Group A - Czechia vs Korea Republic (Group Stage) - Winners</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Anoop M K</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Czechia</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>18</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Group A - Czechia vs Korea Republic (Group Stage) - Winners</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Anoop N</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Korea Republic</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>18</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Group A - Czechia vs Korea Republic (Group Stage) - Winners</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ashish</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Draw</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>18</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Group A - Czechia vs Korea Republic (Group Stage) - Winners</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Bejoy</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Draw</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>18</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Group A - Czechia vs Korea Republic (Group Stage) - Winners</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Gijo</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Czechia</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>18</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Group A - Czechia vs Korea Republic (Group Stage) - Winners</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Jidhulal</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Czechia</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>18</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Group A - Czechia vs Korea Republic (Group Stage) - Winners</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Jimson</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Draw</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>18</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Group A - Czechia vs Korea Republic (Group Stage) - Winners</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Lakshmi M S</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Draw</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>18</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Group A - Czechia vs Korea Republic (Group Stage) - Winners</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Muhammedali</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Czechia</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>18</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Group A - Czechia vs Korea Republic (Group Stage) - Winners</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Nikhil Raj</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Czechia</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>18</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Group A - Czechia vs Korea Republic (Group Stage) - Winners</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Rajeesh</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Czechia</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>18</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Group A - Czechia vs Korea Republic (Group Stage) - Winners</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Rajeev</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Korea Republic</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>18</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Group A - Czechia vs Korea Republic (Group Stage) - Winners</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Saneesh</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Draw</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>18</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Group A - Czechia vs Korea Republic (Group Stage) - Winners</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Sikha</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Czechia</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>18</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Group A - Czechia vs Korea Republic (Group Stage) - Winners</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Sooraj</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Korea Republic</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>18</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Group A - Czechia vs Korea Republic (Group Stage) - Winners</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Vijay</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Draw</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>18</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Group A - Czechia vs Korea Republic (Group Stage) - Winners</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Vineeth</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Czechia</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>18</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Group A - Czechia vs Korea Republic (Group Stage) - Winners</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Vipin M B</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Draw</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>18</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Group A - Czechia vs Korea Republic (Group Stage) - Winners</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Vipin Raj</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Czechia</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
